--- a/input_tool/edu_table_helper_EN_AFG.xlsx
+++ b/input_tool/edu_table_helper_EN_AFG.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yann SAY\Desktop\git\EduAnalysisTool\input_tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A5A56DA-FC78-4F08-9960-9C3AB08C912B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99C3B959-47B9-46FF-840A-9ED11DAE893F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{AD85D784-B454-4039-8455-21301024D336}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{AD85D784-B454-4039-8455-21301024D336}"/>
   </bookViews>
   <sheets>
     <sheet name="access" sheetId="1" r:id="rId1"/>
@@ -144,12 +144,6 @@
     <t>There is a ban preventing child from attending</t>
   </si>
   <si>
-    <t>There is a lack of interest/Education is not a priority either for the child or the household</t>
-  </si>
-  <si>
-    <t>Child participating in income generating activities outside of the home</t>
-  </si>
-  <si>
     <t>No school in the area or school is too far</t>
   </si>
   <si>
@@ -178,6 +172,12 @@
   </si>
   <si>
     <t>% of OoS children</t>
+  </si>
+  <si>
+    <t>Child needs to work at home or on the household's own farm</t>
+  </si>
+  <si>
+    <t>Unable to enroll in school due to recent displacement/return</t>
   </si>
 </sst>
 </file>
@@ -650,7 +650,7 @@
     </row>
     <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>17</v>
@@ -658,10 +658,10 @@
     </row>
     <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -706,10 +706,10 @@
     </row>
     <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" t="s">
         <v>38</v>
-      </c>
-      <c r="B2" t="s">
-        <v>40</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
@@ -721,23 +721,23 @@
         <v>15</v>
       </c>
       <c r="F2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G4" s="5"/>
     </row>
@@ -788,7 +788,7 @@
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>18</v>
@@ -802,7 +802,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>33</v>
@@ -810,15 +810,15 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G5" s="4" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -889,7 +889,7 @@
     </row>
     <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>21</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -961,13 +961,13 @@
     </row>
     <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G3" s="3"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1031,13 +1031,13 @@
     </row>
     <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G3" s="3"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1101,13 +1101,13 @@
     </row>
     <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G3" s="3"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1171,13 +1171,13 @@
     </row>
     <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G3" s="3"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
